--- a/data/trans_dic/IQ2605_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IQ2605_R2-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72,02%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>48,7%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>78,95%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>66,23%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>73,54%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,59; 56,06</t>
+          <t>35,33; 48,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,32; 84,27</t>
+          <t>70,9; 83,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,99; 72,78</t>
+          <t>71,81; 83,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,99; 84,96</t>
+          <t>57,97; 83,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,46; 47,93</t>
+          <t>41,28; 55,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,45; 83,0</t>
+          <t>72,75; 84,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,27; 83,56</t>
+          <t>58,99; 72,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,45; 83,43</t>
+          <t>59,6; 84,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,81; 49,9</t>
+          <t>40,43; 50,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,86; 82,28</t>
+          <t>73,8; 82,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,03; 77,62</t>
+          <t>67,61; 76,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,19; 81,23</t>
+          <t>61,79; 80,98</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>57,55%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>77,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>77,87%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>51,8%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>79,18%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>77,67%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>77,55%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,82; 56,83</t>
+          <t>52,05; 63,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,35; 83,45</t>
+          <t>72,64; 81,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,77; 81,81</t>
+          <t>73,05; 82,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,96; 88,71</t>
+          <t>79,19; 94,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,92; 63,36</t>
+          <t>46,15; 57,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,88; 82,39</t>
+          <t>74,65; 83,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,01; 81,83</t>
+          <t>72,73; 81,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,47; 94,05</t>
+          <t>61,72; 87,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,96; 59,08</t>
+          <t>50,92; 58,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75,15; 81,48</t>
+          <t>74,43; 81,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,57; 80,99</t>
+          <t>74,33; 81,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,5; 89,55</t>
+          <t>75,11; 89,33</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45,66%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72,35%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>85,84%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>68,81%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>51,18%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>68,95%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>84,9%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66,96%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>45,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,06; 57,85</t>
+          <t>39,29; 52,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,25; 74,41</t>
+          <t>66,0; 77,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,04; 89,21</t>
+          <t>80,78; 89,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,23; 81,21</t>
+          <t>54,19; 80,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,78; 52,71</t>
+          <t>44,67; 58,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,53; 77,81</t>
+          <t>62,56; 74,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,63; 89,41</t>
+          <t>80,11; 89,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,4; 79,25</t>
+          <t>47,99; 78,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,78; 53,01</t>
+          <t>44,01; 53,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,27; 74,73</t>
+          <t>66,12; 74,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82,16; 88,26</t>
+          <t>81,88; 88,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,71; 76,84</t>
+          <t>56,42; 75,34</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>61,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66,06%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75,91%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71,31%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>67,94%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>73,97%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69,41%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>61,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,91%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,76; 66,88</t>
+          <t>55,43; 66,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,34; 73,63</t>
+          <t>60,24; 71,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,3; 79,1</t>
+          <t>70,02; 80,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,33; 79,44</t>
+          <t>57,86; 82,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,02; 66,71</t>
+          <t>55,1; 67,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,29; 71,41</t>
+          <t>61,99; 73,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,82; 80,66</t>
+          <t>68,1; 78,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,62; 82,49</t>
+          <t>56,08; 78,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,96; 65,17</t>
+          <t>57,43; 65,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62,35; 70,79</t>
+          <t>63,01; 70,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,04; 78,6</t>
+          <t>71,23; 78,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,31; 78,43</t>
+          <t>61,11; 77,88</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73,23%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>73,6%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>73,23%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,7; 56,96</t>
+          <t>49,8; 55,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,62</t>
+          <t>70,59; 75,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,37; 78,56</t>
+          <t>76,43; 81,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,58; 77,76</t>
+          <t>70,69; 81,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,62; 55,78</t>
+          <t>51,06; 57,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,52; 75,94</t>
+          <t>70,61; 76,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,32; 81,49</t>
+          <t>73,26; 78,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>70,27; 82,03</t>
+          <t>64,42; 77,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,23; 55,57</t>
+          <t>51,22; 55,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,3; 75,34</t>
+          <t>71,27; 75,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75,76; 79,45</t>
+          <t>75,71; 79,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,5; 78,57</t>
+          <t>69,65; 78,26</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>61458</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>114785</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>115107</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23387</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>65259</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>108949</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>86228</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19998</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>61458</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>114785</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>115107</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>43712</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55739; 75132</t>
+          <t>52228; 71514</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99795; 116283</t>
+          <t>104932; 122897</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75499; 94758</t>
+          <t>105781; 123300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16315; 23106</t>
+          <t>18822; 27226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52412; 70856</t>
+          <t>55319; 74071</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>105752; 122852</t>
+          <t>100393; 116383</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>106458; 123090</t>
+          <t>76812; 94509</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20240; 29395</t>
+          <t>16531; 23417</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>112191; 140648</t>
+          <t>113938; 141941</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>211230; 235323</t>
+          <t>211063; 234723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>188789; 215413</t>
+          <t>187617; 213486</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38823; 50711</t>
+          <t>37200; 48756</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>242</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>259</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>120634</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>168385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>172714</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>51704</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>99815</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>156895</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>159059</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30488</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>120634</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>168385</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>172714</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55154</t>
+          <t>30512</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85643</t>
+          <t>82216</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88297; 109495</t>
+          <t>109096; 132161</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>147325; 165373</t>
+          <t>157673; 177777</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149032; 167539</t>
+          <t>162023; 182988</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25147; 34876</t>
+          <t>46555; 55421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>108815; 132808</t>
+          <t>88923; 111012</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>158178; 178824</t>
+          <t>147933; 165338</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161935; 181493</t>
+          <t>148935; 167187</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49060; 58798</t>
+          <t>24296; 34587</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>205014; 237688</t>
+          <t>204862; 235626</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>312047; 338323</t>
+          <t>309046; 338119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>318101; 345483</t>
+          <t>317061; 345777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77902; 91192</t>
+          <t>73720; 87682</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>65174</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142079</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>67358</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>103337</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>129433</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20237</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>65174</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>114607</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>142079</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>45925</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59307; 76137</t>
+          <t>56087; 75143</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93291; 111513</t>
+          <t>104555; 122851</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122015; 136005</t>
+          <t>133700; 147990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15481; 24541</t>
+          <t>22493; 33513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56784; 75241</t>
+          <t>58798; 76472</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>105389; 123253</t>
+          <t>93755; 111086</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>133453; 147982</t>
+          <t>122127; 136192</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23156; 35021</t>
+          <t>13091; 21502</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120121; 145424</t>
+          <t>120735; 146178</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>204307; 230386</t>
+          <t>203826; 230493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>261236; 280621</t>
+          <t>260336; 280252</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42944; 57179</t>
+          <t>38806; 51819</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>48</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>126136</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132982</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>153876</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32515</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>126147</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>137123</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>151371</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32182</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>126136</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>132982</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>153876</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36111</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68293</t>
+          <t>63710</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>115054; 138011</t>
+          <t>114443; 137417</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>125831; 148622</t>
+          <t>121267; 143865</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>139777; 161874</t>
+          <t>141951; 162854</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26117; 36830</t>
+          <t>26379; 37399</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>115663; 137730</t>
+          <t>113695; 138690</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>121363; 143753</t>
+          <t>125126; 148230</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>143576; 163512</t>
+          <t>139361; 160214</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29209; 41106</t>
+          <t>25323; 35594</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>235144; 269027</t>
+          <t>237074; 269974</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>251365; 285378</t>
+          <t>254016; 285754</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>289383; 320208</t>
+          <t>290147; 319092</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59941; 75444</t>
+          <t>55459; 70677</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>373402</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>530759</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>583776</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>136167</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>358579</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>506305</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>526091</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>102905</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>373402</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>530759</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>249353</t>
+          <t>235563</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>336981; 378576</t>
+          <t>351905; 393254</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>486435; 527029</t>
+          <t>511646; 548841</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>507772; 543676</t>
+          <t>563535; 600903</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93844; 111272</t>
+          <t>126085; 145254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>350621; 394190</t>
+          <t>339361; 379085</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>511119; 550397</t>
+          <t>485730; 525483</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>562734; 600860</t>
+          <t>507027; 543833</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>134765; 157301</t>
+          <t>89886; 107975</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>702468; 762083</t>
+          <t>702365; 760534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1007259; 1064264</t>
+          <t>1006721; 1064836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1082965; 1135614</t>
+          <t>1082220; 1134290</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>236071; 263118</t>
+          <t>221415; 248795</t>
         </is>
       </c>
     </row>
